--- a/data/raw/sales/Week 17/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 17/Nexlev/other_channels.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Week 17\Week 17\raw\sales\Week 17\Nexlev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 17\Nexlev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CF2069-DECC-46D1-86EE-0BE4CBBEEA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E5D800-66F4-4041-87A7-70B454D09A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D2C - Nexlev" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="233">
   <si>
     <t>SKU</t>
   </si>
@@ -782,33 +782,39 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -901,7 +907,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -941,17 +947,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1248,442 +1245,442 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="16">
         <v>12</v>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="20">
         <v>23898.31</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="16">
         <v>3</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="20">
         <v>9836.4410000000007</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="16">
         <v>1</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="20">
         <v>1661.0170000000001</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="16">
         <v>2</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="20">
         <v>1435.5930000000001</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="16">
         <v>1</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="20">
         <v>762.71190000000001</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="16">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="20">
         <v>1008.571</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="16">
         <v>1</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="20">
         <v>717.79660000000001</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="16">
         <v>3</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="20">
         <v>2921.1860000000001</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="16">
         <v>1</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="20">
         <v>987.28809999999999</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="16">
         <v>2</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="20">
         <v>268.64409999999998</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="16">
         <v>1</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="20">
         <v>1778.8140000000001</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="19">
-        <v>10</v>
-      </c>
-      <c r="E13" s="23">
+      <c r="D13" s="16">
+        <v>10</v>
+      </c>
+      <c r="E13" s="20">
         <v>18644.07</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="16">
         <v>7</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="20">
         <v>3598.3049999999998</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="16">
         <v>2</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="20">
         <v>2540.6779999999999</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="16">
         <v>2</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="20">
         <v>3049.1529999999998</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="16">
         <v>1</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="20">
         <v>2244.915</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="16">
         <v>1</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="20">
         <v>2065.2539999999999</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="16">
         <v>1</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="20">
         <v>5388.9830000000002</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="16">
         <v>1</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="20">
         <v>2825.7139999999999</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="16">
         <v>1</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="20">
         <v>2514.4070000000002</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="16">
         <v>1</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="20">
         <v>1885.5930000000001</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="16">
         <v>1</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="20">
         <v>12567.29</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="16" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1697,13 +1694,13 @@
       <c r="C24" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="16">
         <v>1</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="20">
         <v>1991.5250000000001</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="16" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1717,13 +1714,13 @@
       <c r="C25" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="16">
         <v>8</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="20">
         <v>10440.68</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="16" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2668,802 +2665,802 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="22">
         <v>4</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="21">
         <v>6335.5929999999998</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="22">
         <v>3</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="21">
         <v>6264.4070000000002</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="21">
         <v>6</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="21">
         <v>3020.3389999999999</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="22">
         <v>4</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="21">
         <v>3661.0169999999998</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="22">
         <v>1</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="21">
         <v>1332.203</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="23">
         <v>2</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="21">
         <v>1150.847</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="21">
         <v>1</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="21">
         <v>2880.5079999999998</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="21">
         <v>1</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="23">
         <v>935.59320000000002</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="21">
         <v>2</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="21">
         <v>1617.143</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="21">
         <v>15</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="21">
         <v>16985.71</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="21">
         <v>1</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="21">
         <v>720.33900000000006</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="21">
         <v>1</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="21">
         <v>900</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="21">
         <v>5</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="21">
         <v>6300.8469999999998</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="21">
         <v>2</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="21">
         <v>2735.5929999999998</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="21">
         <v>2</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="21">
         <v>4055.9319999999998</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="21">
         <v>2</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="21">
         <v>4896.6099999999997</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="21">
         <v>2</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="21">
         <v>3023.7289999999998</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="21">
         <v>2</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="21">
         <v>3600</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="21">
         <v>1</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="21">
         <v>575.42370000000005</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="21">
         <v>1</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="21">
         <v>2880.5079999999998</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="F21" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="21">
         <v>1</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="21">
         <v>1144.915</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="21">
         <v>2</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="21">
         <v>2184.7620000000002</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="21">
         <v>5</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="21">
         <v>5758.4750000000004</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="21">
         <v>1</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="21">
         <v>1439.8309999999999</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="21">
         <v>1</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="21">
         <v>755.93219999999997</v>
       </c>
-      <c r="F26" s="24" t="s">
+      <c r="F26" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="21">
         <v>5</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="21">
         <v>6300.8469999999998</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="21">
         <v>1</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="21">
         <v>1223.729</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="21">
         <v>1</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="21">
         <v>2161.0169999999998</v>
       </c>
-      <c r="F29" s="24" t="s">
+      <c r="F29" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="21">
         <v>2</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="21">
         <v>3023.7289999999998</v>
       </c>
-      <c r="F30" s="24" t="s">
+      <c r="F30" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="21">
         <v>2</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="21">
         <v>3023.7289999999998</v>
       </c>
-      <c r="F31" s="24" t="s">
+      <c r="F31" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="24" t="s">
+      <c r="A32" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="21">
         <v>3</v>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="21">
         <v>3887.288</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="21">
         <v>2</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="21">
         <v>4320.3389999999999</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="21">
         <v>5</v>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="21">
         <v>2355.9319999999998</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
+      <c r="A35" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="21">
         <v>2</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="21">
         <v>5184.7460000000001</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="F35" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="21">
         <v>1</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="21">
         <v>2160.1689999999999</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="21">
         <v>2</v>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="21">
         <v>1177.9659999999999</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="21">
         <v>1</v>
       </c>
-      <c r="E38" s="24">
+      <c r="E38" s="21">
         <v>588.98310000000004</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="21">
         <v>2</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="21">
         <v>3167.797</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D40" s="21">
         <v>7</v>
       </c>
-      <c r="E40" s="24">
+      <c r="E40" s="21">
         <v>1862.712</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F40" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="21">
         <v>2</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="21">
         <v>2159.3220000000001</v>
       </c>
-      <c r="F41" s="24" t="s">
+      <c r="F41" s="21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3507,102 +3504,102 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="24">
         <v>1</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="24">
         <v>1360.1690000000001</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="24">
         <v>2</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="24">
         <v>2469.4920000000002</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="24">
         <v>1</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="24">
         <v>779.66099999999994</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="24">
         <v>1</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="24">
         <v>2458.4749999999999</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="24">
         <v>1</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="24">
         <v>5143.22</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="24" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4691,7 +4688,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:W60"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -4741,1182 +4738,1162 @@
       <c r="W1" s="7"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="16" t="s">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>135</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" t="s">
         <v>136</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" t="s">
         <v>137</v>
       </c>
-      <c r="E2" s="17">
-        <v>5</v>
-      </c>
-      <c r="F2" s="18">
-        <v>3809.32</v>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>5452</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>37989</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>31938</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>28880</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>5929</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>19059</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="18">
-        <v>17702.54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="17">
-        <v>5</v>
-      </c>
-      <c r="F4" s="18">
-        <v>12283.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="17">
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
-      <c r="F5" s="18">
-        <v>2965.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="17">
-        <v>9</v>
-      </c>
-      <c r="F6" s="18">
-        <v>8890.68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7" s="17">
+      <c r="F15">
+        <v>3092</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17">
         <v>2</v>
       </c>
-      <c r="F7" s="18">
-        <v>1693.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="17">
-        <v>16</v>
-      </c>
-      <c r="F8" s="18">
-        <v>20311.86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="17">
+      <c r="F17">
+        <v>5083</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="F19">
+        <v>4571</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26">
         <v>3</v>
       </c>
-      <c r="F9" s="18">
-        <v>4446.6099999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="17">
-        <v>0</v>
-      </c>
-      <c r="F10" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" s="17">
-        <v>0</v>
-      </c>
-      <c r="F11" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="17">
-        <v>0</v>
-      </c>
-      <c r="F12" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E13" s="17">
+      <c r="F26">
+        <v>5336</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
+        <v>5845</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" t="s">
+        <v>167</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+      <c r="F31">
+        <v>5209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34">
+        <v>6</v>
+      </c>
+      <c r="F34">
+        <v>8125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" t="s">
+        <v>175</v>
+      </c>
+      <c r="D35" t="s">
+        <v>176</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" t="s">
+        <v>179</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+      <c r="F36">
+        <v>6946</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38">
+        <v>32</v>
+      </c>
+      <c r="F38">
+        <v>78617</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" t="s">
+        <v>180</v>
+      </c>
+      <c r="C39" t="s">
+        <v>181</v>
+      </c>
+      <c r="D39" t="s">
+        <v>182</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" t="s">
+        <v>183</v>
+      </c>
+      <c r="C40" t="s">
+        <v>184</v>
+      </c>
+      <c r="D40" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" t="s">
+        <v>66</v>
+      </c>
+      <c r="D44" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" t="s">
+        <v>37</v>
+      </c>
+      <c r="E46">
         <v>1</v>
       </c>
-      <c r="F13" s="18">
-        <v>1143.22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="17">
-        <v>14</v>
-      </c>
-      <c r="F14" s="18">
-        <v>25835.59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="17">
-        <v>2</v>
-      </c>
-      <c r="F15" s="18">
-        <v>6015.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="E16" s="17">
-        <v>0</v>
-      </c>
-      <c r="F16" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="17">
-        <v>2</v>
-      </c>
-      <c r="F17" s="18">
-        <v>4998.3100000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="17">
-        <v>0</v>
-      </c>
-      <c r="F18" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="E19" s="17">
-        <v>3</v>
-      </c>
-      <c r="F19" s="18">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" s="17">
-        <v>0</v>
-      </c>
-      <c r="F20" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="E21" s="17">
-        <v>2</v>
-      </c>
-      <c r="F21" s="18">
-        <v>1947.46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="17">
-        <v>0</v>
-      </c>
-      <c r="F22" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="17">
-        <v>0</v>
-      </c>
-      <c r="F23" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="17">
-        <v>5</v>
-      </c>
-      <c r="F24" s="18">
-        <v>11012.71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E25" s="17">
-        <v>0</v>
-      </c>
-      <c r="F25" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="17">
-        <v>2</v>
-      </c>
-      <c r="F26" s="18">
-        <v>3557.63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="17">
-        <v>0</v>
-      </c>
-      <c r="F27" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E28" s="17">
-        <v>0</v>
-      </c>
-      <c r="F28" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" s="17">
-        <v>2</v>
-      </c>
-      <c r="F29" s="18">
-        <v>3330.51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="E30" s="17">
-        <v>0</v>
-      </c>
-      <c r="F30" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="E31" s="17">
-        <v>7</v>
-      </c>
-      <c r="F31" s="18">
-        <v>12155.08</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="17">
-        <v>0</v>
-      </c>
-      <c r="F32" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E33" s="17">
-        <v>0</v>
-      </c>
-      <c r="F33" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="E34" s="17">
-        <v>4</v>
-      </c>
-      <c r="F34" s="18">
-        <v>5416.95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="E35" s="17">
-        <v>0</v>
-      </c>
-      <c r="F35" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="E36" s="17">
-        <v>9</v>
-      </c>
-      <c r="F36" s="18">
-        <v>16263.56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="17">
-        <v>4</v>
-      </c>
-      <c r="F37" s="18">
-        <v>5335.59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E38" s="17">
-        <v>6</v>
-      </c>
-      <c r="F38" s="18">
-        <v>14516.95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="E39" s="17">
-        <v>0</v>
-      </c>
-      <c r="F39" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="E40" s="17">
-        <v>0</v>
-      </c>
-      <c r="F40" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" s="17">
-        <v>0</v>
-      </c>
-      <c r="F41" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" s="17">
-        <v>0</v>
-      </c>
-      <c r="F42" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="17">
-        <v>0</v>
-      </c>
-      <c r="F43" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E44" s="17">
-        <v>0</v>
-      </c>
-      <c r="F44" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="E45" s="17">
+      <c r="F46">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
+        <v>186</v>
+      </c>
+      <c r="C47" t="s">
+        <v>187</v>
+      </c>
+      <c r="D47" t="s">
+        <v>188</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" t="s">
+        <v>108</v>
+      </c>
+      <c r="D49" t="s">
+        <v>109</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" t="s">
+        <v>117</v>
+      </c>
+      <c r="D50" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>189</v>
+      </c>
+      <c r="C51" t="s">
+        <v>190</v>
+      </c>
+      <c r="D51" t="s">
+        <v>191</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52" t="s">
+        <v>130</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" t="s">
+        <v>102</v>
+      </c>
+      <c r="D53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="s">
+        <v>194</v>
+      </c>
+      <c r="C54" t="s">
+        <v>195</v>
+      </c>
+      <c r="D54" t="s">
+        <v>196</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D55" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C56" t="s">
+        <v>198</v>
+      </c>
+      <c r="D56" t="s">
+        <v>199</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" t="s">
+        <v>132</v>
+      </c>
+      <c r="D57" t="s">
+        <v>133</v>
+      </c>
+      <c r="E57">
         <v>1</v>
       </c>
-      <c r="F45" s="18">
-        <v>1185.5899999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B46" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" s="17">
-        <v>0</v>
-      </c>
-      <c r="F46" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="E47" s="17">
-        <v>1</v>
-      </c>
-      <c r="F47" s="18">
-        <v>846.61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E48" s="17">
-        <v>0</v>
-      </c>
-      <c r="F48" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E49" s="17">
-        <v>0</v>
-      </c>
-      <c r="F49" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E50" s="17">
-        <v>0</v>
-      </c>
-      <c r="F50" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="E51" s="17">
-        <v>0</v>
-      </c>
-      <c r="F51" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" s="17">
-        <v>0</v>
-      </c>
-      <c r="F52" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E53" s="17">
-        <v>0</v>
-      </c>
-      <c r="F53" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E54" s="17">
-        <v>0</v>
-      </c>
-      <c r="F54" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="E55" s="17">
-        <v>0</v>
-      </c>
-      <c r="F55" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="E56" s="17">
-        <v>0</v>
-      </c>
-      <c r="F56" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="E57" s="17">
-        <v>0</v>
-      </c>
-      <c r="F57" s="18">
-        <v>0</v>
+      <c r="F57">
+        <v>423</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="E58" s="17">
-        <v>4</v>
-      </c>
-      <c r="F58" s="18">
-        <v>1452.54</v>
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" t="s">
+        <v>200</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="E59" s="17">
-        <v>0</v>
-      </c>
-      <c r="F59" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60" s="16" t="s">
+      <c r="A59" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C59" t="s">
         <v>126</v>
       </c>
-      <c r="D60" s="16" t="s">
+      <c r="D59" t="s">
         <v>201</v>
       </c>
-      <c r="E60" s="17">
-        <v>0</v>
-      </c>
-      <c r="F60" s="18">
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
         <v>0</v>
       </c>
     </row>
@@ -5960,42 +5937,42 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="16">
         <v>2</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="16">
         <v>1131</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="16">
         <v>1</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="16">
         <v>1615</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="17" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6062,393 +6039,393 @@
       <c r="AA1" s="10"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="16">
         <v>4</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="16">
         <v>2587</v>
       </c>
-      <c r="F2" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="21" t="s">
+      <c r="F2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="18" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="16">
         <v>2</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="16">
         <v>1619</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="21" t="s">
+      <c r="F3" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="18" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="16">
         <v>1</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="16">
         <v>1585</v>
       </c>
-      <c r="F4" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="21" t="s">
+      <c r="F4" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="18" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="16">
         <v>2</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="16">
         <v>2881</v>
       </c>
-      <c r="F5" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="21" t="s">
+      <c r="F5" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="18" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="16">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="16">
         <v>2161</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="21" t="s">
+      <c r="F6" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="16">
         <v>1</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="16">
         <v>4610</v>
       </c>
-      <c r="F7" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="21" t="s">
+      <c r="F7" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="16">
         <v>5</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="16">
         <v>11865</v>
       </c>
-      <c r="F8" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="21" t="s">
+      <c r="F8" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="18" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="16">
         <v>3</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="16">
         <v>2718</v>
       </c>
-      <c r="F9" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="21" t="s">
+      <c r="F9" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="16">
         <v>4</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="16">
         <v>6040</v>
       </c>
-      <c r="F10" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="21" t="s">
+      <c r="F10" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="18" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="16">
         <v>3</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="16">
         <v>4347</v>
       </c>
-      <c r="F11" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="21" t="s">
+      <c r="F11" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="18" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="16">
         <v>3</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="16">
         <v>8136</v>
       </c>
-      <c r="F12" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="21" t="s">
+      <c r="F12" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="16">
         <v>4</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="16">
         <v>1628</v>
       </c>
-      <c r="F13" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="21" t="s">
+      <c r="F13" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="18" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="16">
         <v>4</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="16">
         <v>1088</v>
       </c>
-      <c r="F14" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="21" t="s">
+      <c r="F14" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="18" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="16">
         <v>50</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="16">
         <v>38725</v>
       </c>
-      <c r="F15" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="21" t="s">
+      <c r="F15" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="18" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="16">
         <v>40</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="20">
         <v>81355.929999999993</v>
       </c>
-      <c r="F16" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="21" t="s">
+      <c r="F16" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="18" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="27">
         <v>45</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="20">
         <v>104606.1</v>
       </c>
-      <c r="F17" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="21" t="s">
+      <c r="F17" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="18" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="15">
         <v>6</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="20">
         <v>12424.28</v>
       </c>
-      <c r="F18" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="21" t="s">
+      <c r="F18" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>215</v>
       </c>
     </row>
@@ -6484,7 +6461,7 @@
       <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="14" t="s">
@@ -6492,19 +6469,19 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="17" t="s">
         <v>153</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="17">
         <v>1</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="30">
         <v>677</v>
       </c>
       <c r="F2" s="13" t="s">

--- a/data/raw/sales/Week 17/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 17/Nexlev/other_channels.xlsx
@@ -3125,7 +3125,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>ETC-07-WH</t>
         </is>
       </c>
       <c r="D34" s="21" t="n">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="D37" s="21" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>V-01-RG</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="D41" s="21" t="n">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>ET-02</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D4" s="24" t="n">
@@ -6363,7 +6363,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>FBA79347</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>ETC-05</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="C2" s="29" t="inlineStr">
         <is>
-          <t>ETC-04</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
